--- a/artfynd/A 3187-2025 artfynd.xlsx
+++ b/artfynd/A 3187-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91846408</v>
+        <v>111128723</v>
       </c>
       <c r="B2" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Halstjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488941.0079181965</v>
+        <v>488886</v>
       </c>
       <c r="R2" t="n">
-        <v>6918393.18643219</v>
+        <v>6918385</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,53 +760,48 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Alexander Singer, Helena Björnström, Elin Götmark, Brian Johnson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110875634</v>
+        <v>111128736</v>
       </c>
       <c r="B3" t="n">
-        <v>89558</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,13 +811,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488895.148104652</v>
+        <v>488956</v>
       </c>
       <c r="R3" t="n">
-        <v>6918427.653312206</v>
+        <v>6918433</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,27 +861,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Karolin Hård, Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Alexander Singer, Helena Björnström, Elin Götmark, Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110875637</v>
+        <v>111128737</v>
       </c>
       <c r="B4" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,13 +912,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488865.9386778399</v>
+        <v>488864</v>
       </c>
       <c r="R4" t="n">
-        <v>6918441.661805569</v>
+        <v>6918330</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,22 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,36 +958,30 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Karolin Hård</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Karolin Hård, Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Alexander Singer, Helena Björnström, Elin Götmark, Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>111133077</v>
       </c>
       <c r="B5" t="n">
-        <v>77186</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1060,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488815.5456263048</v>
+        <v>488816</v>
       </c>
       <c r="R5" t="n">
-        <v>6918369.954300197</v>
+        <v>6918370</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,19 +1046,9 @@
           <t>2023-07-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,15 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111128676</v>
+        <v>111133080</v>
       </c>
       <c r="B6" t="n">
-        <v>90854</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,21 +1091,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1177,13 +1115,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488863.2228056625</v>
+        <v>488960</v>
       </c>
       <c r="R6" t="n">
-        <v>6918323.422825907</v>
+        <v>6918430</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,39 +1148,30 @@
           <t>2023-07-28</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-07-28</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Singer, Helena Björnström, Elin Götmark, Brian Johnson</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1253,53 +1182,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111133095</v>
+        <v>110875640</v>
       </c>
       <c r="B7" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Halstjärnarna, Jmt</t>
+          <t>Horten V/Stuguhögen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488855.1178614934</v>
+        <v>488839</v>
       </c>
       <c r="R7" t="n">
-        <v>6918260.382519837</v>
+        <v>6918438</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,22 +1247,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,53 +1267,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Brian Johnson, Helena Björnström, Alexander Singer, Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
-        </is>
-      </c>
+          <t>Karolin Hård, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111133092</v>
+        <v>110875634</v>
       </c>
       <c r="B8" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1409,13 +1314,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488883.0372784745</v>
+        <v>488895</v>
       </c>
       <c r="R8" t="n">
-        <v>6918416.564478613</v>
+        <v>6918428</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1439,22 +1344,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,53 +1364,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Brian Johnson, Helena Björnström, Alexander Singer, Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
-        </is>
-      </c>
+          <t>Karolin Hård, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111128636</v>
+        <v>111128714</v>
       </c>
       <c r="B9" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1525,10 +1411,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488865.1112695841</v>
+        <v>488822</v>
       </c>
       <c r="R9" t="n">
-        <v>6918332.691040028</v>
+        <v>6918259</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1558,19 +1444,9 @@
           <t>2023-07-28</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,37 +1477,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111128752</v>
+        <v>111128658</v>
       </c>
       <c r="B10" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1641,10 +1512,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488876.9832665447</v>
+        <v>488771</v>
       </c>
       <c r="R10" t="n">
-        <v>6918271.903031666</v>
+        <v>6918409</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1674,19 +1545,9 @@
           <t>2023-07-28</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,37 +1578,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111133094</v>
+        <v>111128659</v>
       </c>
       <c r="B11" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1757,13 +1613,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488837.7741765007</v>
+        <v>488760</v>
       </c>
       <c r="R11" t="n">
-        <v>6918351.331158265</v>
+        <v>6918459</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1790,19 +1646,9 @@
           <t>2023-07-28</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,12 +1663,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Brian Johnson, Helena Björnström, Alexander Singer, Elin Götmark</t>
+          <t>Alexander Singer, Helena Björnström, Elin Götmark, Brian Johnson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1833,15 +1679,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111128658</v>
+        <v>111128676</v>
       </c>
       <c r="B12" t="n">
-        <v>88489</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,21 +1690,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>2079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1873,10 +1714,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488771.097057931</v>
+        <v>488863</v>
       </c>
       <c r="R12" t="n">
-        <v>6918409.51926557</v>
+        <v>6918324</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1906,19 +1747,9 @@
           <t>2023-07-28</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1949,53 +1780,52 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111128714</v>
+        <v>112550395</v>
       </c>
       <c r="B13" t="n">
-        <v>89558</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1503</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Halstjärnarna, Jmt</t>
+          <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488822.1407714089</v>
+        <v>488886</v>
       </c>
       <c r="R13" t="n">
-        <v>6918259.101433897</v>
+        <v>6918305</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2019,22 +1849,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,35 +1865,38 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alexander Singer, Helena Björnström, Elin Götmark, Brian Johnson</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111128651</v>
+        <v>110875636</v>
       </c>
       <c r="B14" t="n">
-        <v>78081</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,21 +1904,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2105,13 +1928,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488904.3371288842</v>
+        <v>488888</v>
       </c>
       <c r="R14" t="n">
-        <v>6918397.945127899</v>
+        <v>6918477</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2135,22 +1958,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,31 +1978,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Karolin Hård</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alexander Singer, Helena Björnström, Elin Götmark, Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
-        </is>
-      </c>
+          <t>Karolin Hård, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111128649</v>
+        <v>111128751</v>
       </c>
       <c r="B15" t="n">
-        <v>78081</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,21 +2001,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2221,10 +2025,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488938.6706614289</v>
+        <v>488907</v>
       </c>
       <c r="R15" t="n">
-        <v>6918388.557001207</v>
+        <v>6918388</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2254,19 +2058,9 @@
           <t>2023-07-28</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2297,15 +2091,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111128737</v>
+        <v>111128752</v>
       </c>
       <c r="B16" t="n">
-        <v>77186</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,21 +2102,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2337,10 +2126,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488864.171673827</v>
+        <v>488877</v>
       </c>
       <c r="R16" t="n">
-        <v>6918329.448096195</v>
+        <v>6918272</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2370,19 +2159,9 @@
           <t>2023-07-28</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2413,19 +2192,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111128751</v>
+        <v>111133090</v>
       </c>
       <c r="B17" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2453,13 +2227,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488907.5554807374</v>
+        <v>488984</v>
       </c>
       <c r="R17" t="n">
-        <v>6918388.196403931</v>
+        <v>6918458</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2486,19 +2260,9 @@
           <t>2023-07-28</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2513,12 +2277,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alexander Singer, Helena Björnström, Elin Götmark, Brian Johnson</t>
+          <t>Brian Johnson, Helena Björnström, Alexander Singer, Elin Götmark</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2529,15 +2293,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111128736</v>
+        <v>111133091</v>
       </c>
       <c r="B18" t="n">
-        <v>77186</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2545,21 +2304,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2569,13 +2328,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488955.998385791</v>
+        <v>488883</v>
       </c>
       <c r="R18" t="n">
-        <v>6918432.552510571</v>
+        <v>6918417</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2602,19 +2361,9 @@
           <t>2023-07-28</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2629,12 +2378,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alexander Singer, Helena Björnström, Elin Götmark, Brian Johnson</t>
+          <t>Brian Johnson, Helena Björnström, Alexander Singer, Elin Götmark</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2648,16 +2397,11 @@
         <v>111133093</v>
       </c>
       <c r="B19" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2685,10 +2429,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488862.5304402964</v>
+        <v>488862</v>
       </c>
       <c r="R19" t="n">
-        <v>6918394.374450415</v>
+        <v>6918395</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2718,19 +2462,9 @@
           <t>2023-07-28</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2761,15 +2495,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111128638</v>
+        <v>111133094</v>
       </c>
       <c r="B20" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2777,21 +2506,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2801,13 +2530,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488824.9364781507</v>
+        <v>488838</v>
       </c>
       <c r="R20" t="n">
-        <v>6918261.874493847</v>
+        <v>6918351</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2834,19 +2563,9 @@
           <t>2023-07-28</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2861,12 +2580,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alexander Singer, Helena Björnström, Elin Götmark, Brian Johnson</t>
+          <t>Brian Johnson, Helena Björnström, Alexander Singer, Elin Götmark</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2877,37 +2596,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111128723</v>
+        <v>111133095</v>
       </c>
       <c r="B21" t="n">
-        <v>89646</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2917,13 +2631,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488886.6459213104</v>
+        <v>488855</v>
       </c>
       <c r="R21" t="n">
-        <v>6918384.556125979</v>
+        <v>6918261</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2950,19 +2664,9 @@
           <t>2023-07-28</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2977,12 +2681,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alexander Singer, Helena Björnström, Elin Götmark, Brian Johnson</t>
+          <t>Brian Johnson, Helena Björnström, Alexander Singer, Elin Götmark</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2993,15 +2697,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111133080</v>
+        <v>111490764</v>
       </c>
       <c r="B22" t="n">
-        <v>77186</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3009,37 +2708,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Halstjärnarna, Jmt</t>
+          <t>Stuguhögstjärnen, Stuguhögstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488960.1716485709</v>
+        <v>488969</v>
       </c>
       <c r="R22" t="n">
-        <v>6918430.683879814</v>
+        <v>6918422</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3063,22 +2763,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3087,38 +2787,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111490764</v>
+        <v>111133041</v>
       </c>
       <c r="B23" t="n">
-        <v>90678</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3126,38 +2816,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4366</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stuguhögstjärnen (Stuguhögstjärnen), Jmt</t>
+          <t>Halstjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488968.968791491</v>
+        <v>488839</v>
       </c>
       <c r="R23" t="n">
-        <v>6918422.771737494</v>
+        <v>6918475</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3181,22 +2870,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3211,69 +2890,75 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Brian Johnson, Helena Björnström, Alexander Singer, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112550395</v>
+        <v>111498954</v>
       </c>
       <c r="B24" t="n">
-        <v>90914</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Horten, Jmt</t>
+          <t>Stuguhögstjärn, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488886</v>
+        <v>488772</v>
       </c>
       <c r="R24" t="n">
-        <v>6918305</v>
+        <v>6918451</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3311,31 +2996,932 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Sebastian Acker</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Sebastian Acker</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Håkan Blomqvist, Sebastian Acker, Gustaf Nilsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>110875638</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Halstjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>488839</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6918438</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Karolin Hård</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Karolin Hård, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>110875639</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Halstjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>488839</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6918438</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Karolin Hård</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Karolin Hård, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>111128636</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Halstjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>488865</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6918332</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Alexander Singer, Helena Björnström, Elin Götmark, Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>111128638</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Halstjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>488825</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6918262</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Alexander Singer, Helena Björnström, Elin Götmark, Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>91846408</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Jämtlands län, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>488941</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6918393</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2019-10-31</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>110875637</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Halstjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>488866</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6918442</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Karolin Hård</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Karolin Hård, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>111128680</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Halstjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>488971</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6918465</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Alexander Singer, Helena Björnström, Elin Götmark, Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>111128649</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Halstjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>488938</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6918388</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Alexander Singer, Helena Björnström, Elin Götmark, Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>111128651</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Halstjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>488905</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6918398</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Alexander Singer, Helena Björnström, Elin Götmark, Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 3187-2025 artfynd.xlsx
+++ b/artfynd/A 3187-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111128723</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111128736</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111128737</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111133077</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111133080</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1276,6 +1306,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875640</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1373,6 +1408,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875634</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1474,6 +1514,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111128714</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1575,6 +1620,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111128658</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1676,6 +1726,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111128659</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1777,6 +1832,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111128676</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1890,6 +1950,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550395</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1987,6 +2052,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875636</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2088,6 +2158,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111128751</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2189,6 +2264,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111128752</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2290,6 +2370,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111133090</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2391,6 +2476,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111133091</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2492,6 +2582,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111133093</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2593,6 +2688,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111133094</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2694,6 +2794,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111133095</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2802,6 +2907,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111490764</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2903,6 +3013,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111133041</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3012,6 +3127,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111498954</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3114,6 +3234,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875638</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3216,6 +3341,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875639</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3317,6 +3447,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111128636</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3418,6 +3553,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111128638</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3519,6 +3659,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91846408</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3621,6 +3766,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110875637</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3722,6 +3872,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111128680</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3823,6 +3978,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111128649</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3924,8 +4084,47 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111128651</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>